--- a/list-organization-prefered-notif-email-20260922-12h06-saidou.xlsx
+++ b/list-organization-prefered-notif-email-20260922-12h06-saidou.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Utilisateurs\mrazafinirina\Works\Projets\CPS\DB\20260922-Liste-Organization-with-Email-prefered\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC84B955-ECE6-490D-9DA4-156845944528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5723727-E338-4C17-8EEE-1B5C2CF076F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1512" yWindow="1428" windowWidth="17280" windowHeight="9960" xr2:uid="{794322D0-D6F8-43E0-89A5-7FB6748ECC28}"/>
   </bookViews>
@@ -10488,43 +10488,43 @@
         <v>2694004084</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="3" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3">
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="1">
         <v>2694004118</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="4" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4">
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="1">
         <v>2694004310</v>
       </c>
     </row>
